--- a/data/testdata/data.xlsx
+++ b/data/testdata/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\computer\py project\test2\data\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396418CA-DDDF-460D-8423-31FC453B9C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B29146-B5FE-441A-958B-6DBCF058E536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3697" windowWidth="17280" windowHeight="9983" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="login" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>order_number</t>
   </si>
@@ -37,30 +37,10 @@
     <t>test_login2</t>
   </si>
   <si>
-    <t>test_login3</t>
-  </si>
-  <si>
     <t>account</t>
   </si>
   <si>
     <t>passwd</t>
-  </si>
-  <si>
-    <t>13318177872</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wzj958674123</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>wzj958674124</t>
-  </si>
-  <si>
-    <t>wzj958674125</t>
-  </si>
-  <si>
-    <t>wzj958674126</t>
   </si>
   <si>
     <t>errMsg</t>
@@ -68,6 +48,22 @@
   </si>
   <si>
     <t>success</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>123456</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>13311117872</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1331111787</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>133111178721</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -461,16 +457,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -483,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>9</v>
@@ -500,10 +496,10 @@
         <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="3"/>
@@ -517,28 +513,20 @@
         <v>4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="2"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2"/>
